--- a/lucas/import_data/dataset_meta/excel/data_source.xlsx
+++ b/lucas/import_data/dataset_meta/excel/data_source.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -80,16 +80,44 @@
   </si>
   <si>
     <t xml:space="preserve">ec-esdac@jrc.ec.europa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">european environment agency (eea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eu-eea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EU EEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.eea.europa.eu/en</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kongens Nytorv 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copenhagen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">denmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">info@eea.europa.eu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -111,6 +139,20 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2F4052"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A55A9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -154,7 +196,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -163,8 +205,36 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -176,6 +246,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0A55A9"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF2F4052"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -187,37 +317,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -290,74 +420,111 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -365,8 +532,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>